--- a/inputs/user/model_matching.xlsx
+++ b/inputs/user/model_matching.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A17C88-01D5-4112-8570-D08749A0896F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2A0EDD-CCB6-4B61-9035-8FD0A5466E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="225" windowWidth="22965" windowHeight="15480" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="material" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="287">
   <si>
     <t>Own</t>
   </si>
@@ -887,6 +887,15 @@
   </si>
   <si>
     <t>oil</t>
+  </si>
+  <si>
+    <t>Biomass</t>
+  </si>
+  <si>
+    <t>Biomass-Fired Power Plant</t>
+  </si>
+  <si>
+    <t>biomass</t>
   </si>
 </sst>
 </file>
@@ -2193,7 +2202,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -2305,26 +2314,47 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D6" t="s">
+        <v>286</v>
+      </c>
+      <c r="E6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>99</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>98</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>234</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F7" t="s">
         <v>283</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
